--- a/public/templates/examples/A-033-RiskTreatmentAcceptanceDecisionsLog-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-033-RiskTreatmentAcceptanceDecisionsLog-EXAMPLE-S.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="0"/>
   <fonts count="7">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -216,12 +216,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="552450" cy="552450"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -335,7 +335,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -369,7 +369,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/examples/A-033-RiskTreatmentAcceptanceDecisionsLog-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-033-RiskTreatmentAcceptanceDecisionsLog-EXAMPLE-S.xlsx
@@ -4,19 +4,21 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Aptos"/>
@@ -105,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -136,6 +138,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -579,7 +585,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -717,7 +723,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Risk ID</t>
@@ -759,7 +765,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="50.5" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>R-03</t>
@@ -785,19 +791,15 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>2027-04-10</t>
-        </is>
+      <c r="F12" s="12">
+        <v>46122</v>
+      </c>
+      <c r="G12" s="12">
+        <v>46487</v>
       </c>
       <c r="H12" s="8" t="inlineStr"/>
     </row>
-    <row r="13">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>R-05</t>
@@ -823,15 +825,11 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>2027-04-10</t>
-        </is>
+      <c r="F13" s="12">
+        <v>46122</v>
+      </c>
+      <c r="G13" s="12">
+        <v>46487</v>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
@@ -839,7 +837,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="66.4" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>R-07</t>
@@ -865,15 +863,11 @@
           <t>Tracy Holloway, Director</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
+      <c r="F14" s="12">
+        <v>46122</v>
+      </c>
+      <c r="G14" s="12">
+        <v>46305</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
@@ -881,7 +875,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="50.5" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>R-09</t>
@@ -907,15 +901,11 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>2026-02-15</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>2027-02-15</t>
-        </is>
+      <c r="F15" s="12">
+        <v>46068</v>
+      </c>
+      <c r="G15" s="12">
+        <v>46433</v>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
@@ -930,7 +920,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
+    <row r="18" ht="34.7" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Risk ID</t>
@@ -952,7 +942,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="34.7" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>R-07</t>
@@ -963,10 +953,8 @@
           <t>Tracy Holloway, Director</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
+      <c r="C19" s="12">
+        <v>46305</v>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
@@ -1054,10 +1042,8 @@
           <t>Tracy Holloway</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="D28" s="13">
+        <v>46174</v>
       </c>
     </row>
     <row r="30">
@@ -1089,16 +1075,14 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="34.7" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="B32" s="12">
+        <v>46174</v>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
@@ -1135,7 +1119,8 @@
     <mergeCell ref="A26:J26"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>